--- a/SGC-CKN/Excel/8ff1f678-ed40-4bbc-96f8-3da21b8d7738_Cọc_khoan_nhồi_-_Trụ_P17g_C8_D2000_17-03-2026.xlsx
+++ b/SGC-CKN/Excel/8ff1f678-ed40-4bbc-96f8-3da21b8d7738_Cọc_khoan_nhồi_-_Trụ_P17g_C8_D2000_17-03-2026.xlsx
@@ -29,7 +29,7 @@
     <t>Tên bộ phận</t>
   </si>
   <si>
-    <t>Cọc khoan nhồi - Trụ P17g</t>
+    <t>Cọc khoan nhồi - Trụ P479</t>
   </si>
   <si>
     <t>Số hiệu cọc</t>
